--- a/Teste_de_sistemas/Trabalhos/PROVA_API_SIMPSONS_DESI_25_1_VITOR_RAZIA_BUBOLS/02_matriz_de_testes/Matriz_de_Testes_Vitor_Razia_Bubols.xlsx
+++ b/Teste_de_sistemas/Trabalhos/PROVA_API_SIMPSONS_DESI_25_1_VITOR_RAZIA_BUBOLS/02_matriz_de_testes/Matriz_de_Testes_Vitor_Razia_Bubols.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vitor_bubols\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vitor_bubols\SENAI_FASE3\Teste_de_sistemas\Trabalhos\PROVA_API_SIMPSONS_DESI_25_1_VITOR_RAZIA_BUBOLS\02_matriz_de_testes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BD2A0C-0257-45BE-B1D3-9059AC4F70F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C332A158-EFD7-4539-8B2E-3915B12774E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="106">
   <si>
     <t>Suíte</t>
   </si>
@@ -303,6 +303,54 @@
   </si>
   <si>
     <t>Retorna a página inicial da lista de personagens</t>
+  </si>
+  <si>
+    <t>EVID_CHAR_GET_characters_LIST_P1</t>
+  </si>
+  <si>
+    <t>EVID_CHAR_GET_characters_LIST_P2</t>
+  </si>
+  <si>
+    <t>EVID_CHAR_GET_characters_BUSID</t>
+  </si>
+  <si>
+    <t>EVID_CHAR_GET_characters_BUSID_INEXISTENTE</t>
+  </si>
+  <si>
+    <t>EVID_NEG_GET_characters_INVALID</t>
+  </si>
+  <si>
+    <t>EVID_EPISODES_GET_episodes_LIST_P1</t>
+  </si>
+  <si>
+    <t>EVID_EPISODES_GET_episodes_LIST_P2</t>
+  </si>
+  <si>
+    <t>EVID_EPISODES_GET_episodes_BUSID</t>
+  </si>
+  <si>
+    <t>EVID_EPISODES_GET_episodes_BUSI_INEXISTENTE</t>
+  </si>
+  <si>
+    <t>EVID_NEG_GET_episodes_NEGATIVA</t>
+  </si>
+  <si>
+    <t>EVID_LOC_GET_locations_LIST_P1</t>
+  </si>
+  <si>
+    <t>EVID_LOC_GET_locations_LIST_P2</t>
+  </si>
+  <si>
+    <t>EVID_LOC_GET_locations_BUSID</t>
+  </si>
+  <si>
+    <t>EVID_LOC_GET_locations_BUSID_INEXISTENTE</t>
+  </si>
+  <si>
+    <t>EVID_IMG_GET_images_TESTE_1</t>
+  </si>
+  <si>
+    <t>EVID_IMG_GET_images_TESTE_2</t>
   </si>
 </sst>
 </file>
@@ -751,7 +799,7 @@
     <col min="7" max="7" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -819,7 +867,7 @@
         <v>66</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>79</v>
@@ -854,7 +902,7 @@
         <v>66</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>72</v>
@@ -889,7 +937,7 @@
         <v>66</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>70</v>
@@ -924,7 +972,7 @@
         <v>66</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>71</v>
@@ -959,7 +1007,7 @@
         <v>66</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>80</v>
@@ -994,7 +1042,7 @@
         <v>66</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>72</v>
@@ -1029,7 +1077,7 @@
         <v>66</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>76</v>
@@ -1064,7 +1112,7 @@
         <v>66</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>77</v>
@@ -1099,7 +1147,7 @@
         <v>66</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>78</v>
@@ -1134,7 +1182,7 @@
         <v>66</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>72</v>
@@ -1169,7 +1217,7 @@
         <v>66</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>82</v>
@@ -1204,7 +1252,7 @@
         <v>66</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>77</v>
@@ -1239,7 +1287,7 @@
         <v>66</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="K14" s="8" t="s">
         <v>85</v>
@@ -1274,7 +1322,7 @@
         <v>66</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="K15" s="8" t="s">
         <v>88</v>
@@ -1309,7 +1357,7 @@
         <v>66</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="K16" s="12" t="s">
         <v>89</v>
@@ -1344,7 +1392,7 @@
         <v>66</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="K17" s="12" t="s">
         <v>89</v>
